--- a/extenbooks/XS002.xlsx
+++ b/extenbooks/XS002.xlsx
@@ -529,7 +529,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B78"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -778,7 +778,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>## Methodology</t>
+          <t>## REVIEW 2026-07 (WP-E Group A) — anchor clarification + Khanjian-dict caveat</t>
         </is>
       </c>
     </row>
@@ -790,31 +790,39 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>XS002 cross-validates the project's primary exploitation rate series S506 (`e = S*/V*`) against Khanjian's (1988, 1989) alternative computation. Khanjian re-estimated S*/V* using a different treatment of unincorporated income (treating it ALL as profit), yielding estimates ~20% higher than Shaikh &amp; Tonak's primary measure. The cross-validation stores 5 benchmark-year comparisons (1958, 1963, 1967, 1972, 1977 — matching the BEA IO benchmark years used elsewhere in the project) with columns: S506 value, Khanjian's `e_star_rev` (revised money form), Khanjian's `e_rev` (revised labor-value form), and the percent gap between S506 and Khanjian's estimates. The legacy script is `code/A##_analytical/A08_khanjian_crossvalidation.py`. Khanjian's values are hardcoded from book Table 5.12 (5 benchmark years); S506 values come from `data/final/S506.csv`. This is a pure analytical composition with no new external source file beyond the book digitization.</t>
+          <t>The **validated column XS002-A is S506-A** (the rate of surplus value S\*/V\*), NOT the Khanjian</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>gap. XS002-A reproduces book **Table I.1 Line 23** (S\*/V\*, Sources = Table H.1) **EXACTLY** at all</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The substantive book framing is the contrast between consistent and inconsistent procedures. The verbatim primary anchor is **"Khanjian (1989) using consistent procedure: Value and price rates of surplus value differ by only 6%-9%. Price-value deviations have minor effects on aggregate measures (Section 5.10, Table 5.12, Figure 5.25)."** (ST 1994 Ch7 §7.3, p.223). The methodology contrast with Wolff is **"Khanjian's S*/V* uniformly lower than S/V by 6%-9% (Khanjian 1988, p. 109, table 19). Wolff's inconsistent procedure biases money rate S*/V* upward by 12%-15% (sum of two differences)."** (ST 1994 Ch7 §7.3, p.223). The formal derivation Khanjian uses comes from Appendix I: **"Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1."** (ST 1994 Appendix I, p.323). The Appendix I Table I.1 numeric trajectory XS002's cross-validation must reproduce is **"Exploitation rate ratio (eu/ep): 1948: 0.80 (unproductive 20% less exploited); 1960: 0.89; 1972: 0.92; 1980: 0.92; 1989: 0.97 (3% less). Convergence: Exploitation rates converging. Both rising, but unproductive rising faster."** (ST 1994 Appendix I Table I.1, pp.330-331).</t>
+          <t>five benchmark years (1958 2.01, 1963 2.07, 1967 2.10, 1972 1.99, 1977 2.10; abs err 0.0000 across</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>the whole 1948-1989 line). Re-anchored: `validation_source` → book Table I.1 Line 23;</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The implementation finds: our S506 vs Khanjian's `e_star_rev` shows gaps of 19-31% across the 5 benchmark years. Direction matches the book — Khanjian is higher than ST. Magnitude is slightly larger than the book's reported "~20%" because Khanjian's revisions also use updated NIPA vintages relative to the book's published S506 reference. Validator PASS: all 5 gaps are positive (Khanjian &gt; ST) and &lt; 50% (rule-of-thumb upper bound). The reason a Khanjian-style cross-validation is the right consistency check — rather than a Wolff-style one — is that Khanjian uses a consistent procedure (sector-level value-added decomposition under the productive/unproductive boundary) while Wolff's symmetric/inconsistent treatment biases S*/V* upward by 12-15% (the sum of Wolff's 4-8% bias and Khanjian's 6-9% Khanjian-vs-ST gap). XS002 therefore stands as an internal consistency check that the project's S506 falls in the expected band relative to a known consistent alternative.</t>
+          <t>validator_class → **book**; refvals unchanged (they already equal the book). No divergence needed.</t>
         </is>
       </c>
     </row>
@@ -826,19 +834,23 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>## Sources</t>
+          <t>**Caveat (flagged, not fixed):** the P02's `KHANJIAN` dict (`e_star_rev` = 2.445, 2.467, … labelled</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>"Table 5.12") runs ~20% ABOVE S506, which **contradicts the book text** (§7.3, p.223: Khanjian's</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_25/full_transcription.md` (Ch7 §7.3 p.223 — Khanjian 6-9% benchmark, Wolff 12-15% bias); `chunk_35/full_transcription.md` (Appendix I, Table I.1 — formal derivation of `eu` and benchmark numeric values)</t>
+          <t>S\*/V\* is **6-9% LOWER** than S/V; it is Wolff's procedure that biases +12-15% upward). Those</t>
         </is>
       </c>
     </row>
@@ -846,7 +858,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>- Book tables: Table 5.12 (Khanjian comparison values, p.~123); Figure 5.25 (Section 5.10 visual); Appendix I Table I.1 (Rates of Exploitation of Unproductive Workers, 1948-89 — 25-step annual calculation methodology); the project's hardcoded benchmark values for 1958/1963/1967/1972/1977</t>
+          <t>higher `e_star_rev` values look like a mis-transcription of Table 5.12 (or Wolff-form figures) and</t>
         </is>
       </c>
     </row>
@@ -854,7 +866,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>- External sources: Khanjian (1988, p.109 table 19 — the 6-9% deviation envelope); Khanjian (1989) — consistent procedure; Wolff (1977b, p.103 table 3, lines 1 and 3 — the symmetric/inconsistent comparator)</t>
+          <t>are a **diagnostic side-column, not the validated quantity**. The "gap 19-31%" narrative below rests</t>
         </is>
       </c>
     </row>
@@ -862,151 +874,135 @@
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>- Upstream series: S506 (rate of surplus value)</t>
+          <t>on that suspect column; a future pass should re-extract Table 5.12 to confirm/replace it.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>- Code: `code/A##_analytical/A08_khanjian_crossvalidation.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad)</t>
-        </is>
-      </c>
+      <c r="B43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>## Methodology</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>## Reference values</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>XS002 cross-validates the project's primary exploitation rate series S506 (`e = S*/V*`) against Khanjian's (1988, 1989) alternative computation. Khanjian re-estimated S*/V* using a different treatment of unincorporated income (treating it ALL as profit), yielding estimates ~20% higher than Shaikh &amp; Tonak's primary measure. The cross-validation stores 5 benchmark-year comparisons (1958, 1963, 1967, 1972, 1977 — matching the BEA IO benchmark years used elsewhere in the project) with columns: S506 value, Khanjian's `e_star_rev` (revised money form), Khanjian's `e_rev` (revised labor-value form), and the percent gap between S506 and Khanjian's estimates. The legacy script is `code/A##_analytical/A08_khanjian_crossvalidation.py`. Khanjian's values are hardcoded from book Table 5.12 (5 benchmark years); S506 values come from `data/final/S506.csv`. This is a pure analytical composition with no new external source file beyond the book digitization.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>- 5 benchmark years: 1958, 1963, 1967, 1972, 1977</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>- Observed gap range (S506 vs Khanjian e_star_rev): **19-31%**</t>
+          <t>The substantive book framing is the contrast between consistent and inconsistent procedures. The verbatim primary anchor is **"Khanjian (1989) using consistent procedure: Value and price rates of surplus value differ by only 6%-9%. Price-value deviations have minor effects on aggregate measures (Section 5.10, Table 5.12, Figure 5.25)."** (ST 1994 Ch7 §7.3, p.223). The methodology contrast with Wolff is **"Khanjian's S*/V* uniformly lower than S/V by 6%-9% (Khanjian 1988, p. 109, table 19). Wolff's inconsistent procedure biases money rate S*/V* upward by 12%-15% (sum of two differences)."** (ST 1994 Ch7 §7.3, p.223). The formal derivation Khanjian uses comes from Appendix I: **"Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1."** (ST 1994 Appendix I, p.323). The Appendix I Table I.1 numeric trajectory XS002's cross-validation must reproduce is **"Exploitation rate ratio (eu/ep): 1948: 0.80 (unproductive 20% less exploited); 1960: 0.89; 1972: 0.92; 1980: 0.92; 1989: 0.97 (3% less). Convergence: Exploitation rates converging. Both rising, but unproductive rising faster."** (ST 1994 Appendix I Table I.1, pp.330-331).</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>- Direction: Khanjian &gt; ST at every benchmark year (PASS)</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>- Validator: all 5 gaps positive and &lt; 50% rule-of-thumb (PASS)</t>
+          <t>The implementation finds: our S506 vs Khanjian's `e_star_rev` shows gaps of 19-31% across the 5 benchmark years. Direction matches the book — Khanjian is higher than ST. Magnitude is slightly larger than the book's reported "~20%" because Khanjian's revisions also use updated NIPA vintages relative to the book's published S506 reference. Validator PASS: all 5 gaps are positive (Khanjian &gt; ST) and &lt; 50% (rule-of-thumb upper bound). The reason a Khanjian-style cross-validation is the right consistency check — rather than a Wolff-style one — is that Khanjian uses a consistent procedure (sector-level value-added decomposition under the productive/unproductive boundary) while Wolff's symmetric/inconsistent treatment biases S*/V* upward by 12-15% (the sum of Wolff's 4-8% bias and Khanjian's 6-9% Khanjian-vs-ST gap). XS002 therefore stands as an internal consistency check that the project's S506 falls in the expected band relative to a known consistent alternative.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>- **Book Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3, p.223)</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>- **Book Wolff comparator**: 12-15% upward bias in money S*/V* from inconsistent symmetric procedure</t>
+          <t>## Sources</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>- **Appendix I Table I.1 numeric trajectory** (validation target): eu/ep ratio 0.80 (1948) → 0.97 (1989) — converging</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>- Validator `expected_range`: not yet populated; `tolerance_class: rate_series`</t>
+          <t>- KB chunks: `Inputs/Shaikh Tonak/Knowledge_Base/HDARP_Extractions/1994_Measuring_Wealth/chunk_25/full_transcription.md` (Ch7 §7.3 p.223 — Khanjian 6-9% benchmark, Wolff 12-15% bias); `chunk_35/full_transcription.md` (Appendix I, Table I.1 — formal derivation of `eu` and benchmark numeric values)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>- Book tables: Table 5.12 (Khanjian comparison values, p.~123); Figure 5.25 (Section 5.10 visual); Appendix I Table I.1 (Rates of Exploitation of Unproductive Workers, 1948-89 — 25-step annual calculation methodology); the project's hardcoded benchmark values for 1958/1963/1967/1972/1977</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>## Known issues</t>
+          <t>- External sources: Khanjian (1988, p.109 table 19 — the 6-9% deviation envelope); Khanjian (1989) — consistent procedure; Wolff (1977b, p.103 table 3, lines 1 and 3 — the symmetric/inconsistent comparator)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>- Upstream series: S506 (rate of surplus value)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>- **Construction steps not specified in registry** (empty array) — relies on legacy standalone script `A08_khanjian_crossvalidation.py`</t>
+          <t>- Code: `code/A##_analytical/A08_khanjian_crossvalidation.py` (legacy standalone analytical script — predates the standard L01/P02/V03 triad)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>- **Khanjian method details paraphrased**, not directly extracted from Khanjian's original 1988/1989 papers — the project relies on book Table 5.12 hardcoded values and the book's narrative summary in §5.10 / §7.3</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>- **Alternative decomposition path not yet documented** in technical detail — the project knows what Khanjian's answer is but not the full sequence of his computation</t>
+          <t>## Reference values</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>- **5 benchmark years only**: matches BEA IO benchmark coverage but is a small validation cross-section</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>- **Gap 19-31% vs book's ~20%**: magnitude slightly larger because Khanjian's revisions use updated NIPA vintages relative to the book's published S506; direction matches</t>
+          <t>- 5 benchmark years: 1958, 1963, 1967, 1972, 1977</t>
         </is>
       </c>
     </row>
@@ -1014,7 +1010,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>- **Legacy script not yet migrated** to the standard L01_XS002 / P02_XS002 / V03_XS002 triad</t>
+          <t>- Observed gap range (S506 vs Khanjian e_star_rev): **19-31%**</t>
         </is>
       </c>
     </row>
@@ -1022,31 +1018,39 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>- **No EPR yet authored** for XS002 (Stage 4 work)</t>
+          <t>- Direction: Khanjian &gt; ST at every benchmark year (PASS)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>- Validator: all 5 gaps positive and &lt; 50% rule-of-thumb (PASS)</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>## Cross-references</t>
+          <t>- **Book Khanjian benchmark**: 6-9% deviation in S*/V* between price and value forms (ST 1994 Ch7 §7.3, p.223)</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>- **Book Wolff comparator**: 12-15% upward bias in money S*/V* from inconsistent symmetric procedure</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>- Upstream: S506 (rate of surplus value)</t>
+          <t>- **Appendix I Table I.1 numeric trajectory** (validation target): eu/ep ratio 0.80 (1948) → 0.97 (1989) — converging</t>
         </is>
       </c>
     </row>
@@ -1054,55 +1058,55 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>- Related decompositions: XS001 (social burden rate — same family of analytical consistency checks); S701/S702/S703 (the value-price-deviation framework Khanjian's benchmark anchors)</t>
+          <t>- Validator `expected_range`: not yet populated; `tolerance_class: rate_series`</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>- Related external: Khanjian (1988, 1989); Wolff (1977a, 1977b, 1979, 1987); Sharpe (1982b); Mohun (2005) — the broader cross-study consistency network</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>- Book derivation: Section 5.10 (Khanjian comparison); Appendix I (formal eu derivation); Ch7 §§7.3-7.4 (consistent vs inconsistent procedure critique)</t>
+          <t>## Known issues</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>- Related project DPRs: S703 (value-price deviations — both rely on the same Khanjian 6-9% benchmark for interpretive grounding)</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>- **Construction steps not specified in registry** (empty array) — relies on legacy standalone script `A08_khanjian_crossvalidation.py`</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>## Provenance trail</t>
+          <t>- **Khanjian method details paraphrased**, not directly extracted from Khanjian's original 1988/1989 papers — the project relies on book Table 5.12 hardcoded values and the book's narrative summary in §5.10 / §7.3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>- **Alternative decomposition path not yet documented** in technical detail — the project knows what Khanjian's answer is but not the full sequence of his computation</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>- **Original research**: `Technical/research/XS002_research.json`, researcher `agent`, 2026-05-16; verbatim quotes added 2026-05-23 (`stage1_cohort3_S901AS001AS002`) — sourced from chunk_25 (Ch7 §7.3 Khanjian/Wolff references) and chunk_35 (Appendix I formal derivation + Table I.1 trajectory)</t>
+          <t>- **5 benchmark years only**: matches BEA IO benchmark coverage but is a small validation cross-section</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1114,117 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 25/35 + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+          <t>- **Gap 19-31% vs book's ~20%**: magnitude slightly larger because Khanjian's revisions use updated NIPA vintages relative to the book's published S506; direction matches</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
+        <is>
+          <t>- **Legacy script not yet migrated** to the standard L01_XS002 / P02_XS002 / V03_XS002 triad</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>- **No EPR yet authored** for XS002 (Stage 4 work)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr"/>
+      <c r="B80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>## Cross-references</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr"/>
+      <c r="B82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>- Upstream: S506 (rate of surplus value)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>- Related decompositions: XS001 (social burden rate — same family of analytical consistency checks); S701/S702/S703 (the value-price-deviation framework Khanjian's benchmark anchors)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>- Related external: Khanjian (1988, 1989); Wolff (1977a, 1977b, 1979, 1987); Sharpe (1982b); Mohun (2005) — the broader cross-study consistency network</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>- Book derivation: Section 5.10 (Khanjian comparison); Appendix I (formal eu derivation); Ch7 §§7.3-7.4 (consistent vs inconsistent procedure critique)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>- Related project DPRs: S703 (value-price deviations — both rely on the same Khanjian 6-9% benchmark for interpretive grounding)</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>## Provenance trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>- **Original research**: `Technical/research/XS002_research.json`, researcher `agent`, 2026-05-16; verbatim quotes added 2026-05-23 (`stage1_cohort3_S901AS001AS002`) — sourced from chunk_25 (Ch7 §7.3 Khanjian/Wolff references) and chunk_35 (Appendix I formal derivation + Table I.1 trajectory)</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>- **DPR enriched**: 2026-05-23 by Stage-3 cohort-1 ingestion agent (cohort agent 4); sources read = research JSON + KB chunks 25/35 + registry entry + project CLAUDE.md (AS-prefix framing mandate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
         <is>
           <t>- **Anu Framework stage**: Stage 3 INGESTION (cohort 1, failing chapters); ingestion gate IDs P31/P32</t>
         </is>
@@ -1133,12 +1241,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="51" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1166,12 +1274,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Khanjian (1989) using consistent procedure: Value and price rates of surplus value differ by only 6%-9%. Price-value deviations have minor effects on aggregate measures (Section 5.10, Table 5.12, Figure 5.25).</t>
+          <t>REVIEW 2026-07 (WP-E Group A) STUDY ANCHOR. XS002-A (the validated column) equals S506-A, the rate of surplus value S*/V*, which reproduces book Table I.1 Line 23 (Sources: Table H.1) EXACTLY at every benchmark year (verified abs err 0.0000). Re-anchored off own-chopped onto this printed book Line 23. NB: the Khanjian e_star_rev figures (2.445 etc.) carried in the P02 as 'Table 5.12' are a separate diagnostic; the book text (Ch7 s7.3) states Khanjian's S*/V* runs 6-9% LOWER than S/V, so those higher e_star_rev values should be treated with caution and are NOT the validated quantity.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994</t>
+          <t>ST 1994, Appendix I, Table I.1, Line 23 (S*/V*, from Table H.1); Chapter 7 s7.3 folio 223</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1291,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Khanjian's S*/V* uniformly lower than S/V by 6%-9% (Khanjian 1988, p. 109, table 19). Wolff's inconsistent procedure biases money rate S*/V* upward by 12%-15% (sum of two differences).</t>
+          <t>Khanjian (1989) using consistent procedure: Value and price rates of surplus value differ by only 6%-9%. Price-value deviations have minor effects on aggregate measures (Section 5.10, Table 5.12, Figure 5.25).</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1200,7 +1308,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1.</t>
+          <t>Khanjian's S*/V* uniformly lower than S/V by 6%-9% (Khanjian 1988, p. 109, table 19). Wolff's inconsistent procedure biases money rate S*/V* upward by 12%-15% (sum of two differences).</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1217,7 +1325,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Exploitation rate ratio (eu/ep): 1948: 0.80 (unproductive 20% less exploited); 1960: 0.89; 1972: 0.92; 1980: 0.92; 1989: 0.97 (3% less). Convergence: Exploitation rates converging. Both rising, but unproductive rising faster.</t>
+          <t>Main Formula: (1 + eu) / (1 + ep) approx (hu/hp) / (ecu/ecp). Known: ep = S*/V* (rate of surplus value for productive workers). Solve for eu: eu = (hu/hp) / (ecu/ecp) . [1 + S*/V*] - 1.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1229,34 +1337,34 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>methodology_derived</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>XS002 is a derived analytical series performing a cross-validation of S506 (Rate of Surplus Value, e = S*/V*) against an alternative computation method attributed to Khanjian. This serves as an internal consistency check for the exploitation rate estimates.</t>
+          <t>Exploitation rate ratio (eu/ep): 1948: 0.80 (unproductive 20% less exploited); 1960: 0.89; 1972: 0.92; 1980: 0.92; 1989: 0.97 (3% less). Convergence: Exploitation rates converging. Both rising, but unproductive rising faster.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>series_registry.json (XS002 definition)</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>construction_reference</t>
+          <t>methodology_derived</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Registry describes XS002 as 'cross-check of S506 vs alternative method' with source_type 'analytical'. The legacy construction script is A08_khanjian_crossvalidation.py. Units are ratio. The series covers 1948-2024.</t>
+          <t>XS002 is a derived analytical series performing a cross-validation of S506 (Rate of Surplus Value, e = S*/V*) against an alternative computation method attributed to Khanjian. This serves as an internal consistency check for the exploitation rate estimates.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>series_registry.json</t>
+          <t>series_registry.json (XS002 definition)</t>
         </is>
       </c>
     </row>
@@ -1268,12 +1376,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Khanjian method likely computes the rate of surplus value through an alternative decomposition path — possibly arriving at S*/V* via different intermediate aggregations of the IO accounts. The cross-validation compares this alternative result against the primary S506 series to verify consistency.</t>
+          <t>Registry describes XS002 as 'cross-check of S506 vs alternative method' with source_type 'analytical'. The legacy construction script is A08_khanjian_crossvalidation.py. Units are ratio. The series covers 1948-2024.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>series_registry.json; ST_1994 methodology context</t>
+          <t>series_registry.json</t>
         </is>
       </c>
     </row>
@@ -1285,33 +1393,41 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>The Khanjian method likely computes the rate of surplus value through an alternative decomposition path — possibly arriving at S*/V* via different intermediate aggregations of the IO accounts. The cross-validation compares this alternative result against the primary S506 series to verify consistency.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>series_registry.json; ST_1994 methodology context</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>construction_reference</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Key input: S506 (Rate of Surplus Value). The construction array in the registry is empty, indicating this was handled by a standalone analytical script rather than the standard pipeline. Status is book_period_validated, confirming the cross-check passed for the original 1948-1989 period.</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>series_registry.json</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>VERBATIM QUOTES (top-level)</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr"/>
-      <c r="C11" s="4" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
+      <c r="B12" s="4" t="inlineStr"/>
+      <c r="C12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
@@ -1327,7 +1443,7 @@
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>223</t>
         </is>
       </c>
     </row>
@@ -1336,36 +1452,37 @@
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
           <t>330-331</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="17"/>
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>methodology_summary</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>Cross-validation analytical series comparing S506 (Rate of Surplus Value) against the Khanjian alternative computation method. Legacy script: A08_khanjian_crossvalidation.py.</t>
         </is>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>known_issues:</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1373,7 +1490,7 @@
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Khanjian method details not yet extracted from knowledge base</t>
+          <t>Construction steps not specified in registry (empty array) — relies on legacy script</t>
         </is>
       </c>
     </row>
@@ -1381,41 +1498,49 @@
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
+          <t>Khanjian method details not yet extracted from knowledge base</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>Alternative decomposition path not yet documented</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>cross_references:</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
         <is>
           <t>S506</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>citations:</t>
-        </is>
-      </c>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>citations:</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
